--- a/data/user_records.xlsx
+++ b/data/user_records.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="366">
   <si>
     <t>CB ILEKA</t>
   </si>
@@ -1054,6 +1054,93 @@
   </si>
   <si>
     <t>This is a stand alone test</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>TASK TEST ISRAEL</t>
+  </si>
+  <si>
+    <t>This is a test to see if this will work fine</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>TEST DOD0</t>
+  </si>
+  <si>
+    <t>TEST DOD0 1</t>
+  </si>
+  <si>
+    <t>TEST KEN</t>
+  </si>
+  <si>
+    <t>TEST FRED</t>
+  </si>
+  <si>
+    <t>TEST FELI</t>
+  </si>
+  <si>
+    <t>THIS IS FELI TEST</t>
+  </si>
+  <si>
+    <t>Email notification</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>TEST escalation</t>
+  </si>
+  <si>
+    <t>this is a test to see escalation</t>
+  </si>
+  <si>
+    <t>TESTESCALATION</t>
+  </si>
+  <si>
+    <t>TEST TO SEE</t>
+  </si>
+  <si>
+    <t>TEST MERGE 1</t>
+  </si>
+  <si>
+    <t>TEST MERGE 2</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>cami tramis</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>Test ticket</t>
+  </si>
+  <si>
+    <t>this is a test to see</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>DADA</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>TEST Vacances</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-25</t>
   </si>
 </sst>
 </file>
@@ -1432,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="19.7109375"/>
@@ -5403,6 +5490,446 @@
         <v>253</v>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="B199" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="C199" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D199" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E199" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F199" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="B200" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="C200" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="D200" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E200" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F200" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="B201" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="C201" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="D201" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E201" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F201" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B202" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="C202" t="s" s="0">
+        <v>342</v>
+      </c>
+      <c r="D202" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E202" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F202" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B203" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="C203" t="s" s="0">
+        <v>343</v>
+      </c>
+      <c r="D203" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E203" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F203" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B204" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="C204" t="s" s="0">
+        <v>344</v>
+      </c>
+      <c r="D204" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E204" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F204" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B205" t="s" s="0">
+        <v>345</v>
+      </c>
+      <c r="C205" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="D205" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E205" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F205" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B206" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="C206" t="s" s="0">
+        <v>262</v>
+      </c>
+      <c r="D206" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E206" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F206" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="B207" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="C207" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="D207" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E207" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F207" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B208" t="s" s="0">
+        <v>349</v>
+      </c>
+      <c r="C208" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="D208" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E208" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F208" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B209" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="C209" t="s" s="0">
+        <v>350</v>
+      </c>
+      <c r="D209" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E209" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F209" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B210" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="C210" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="D210" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E210" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F210" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B211" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="C211" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="D211" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E211" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F211" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="0">
+        <v>348</v>
+      </c>
+      <c r="B212" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="C212" t="s" s="0">
+        <v>354</v>
+      </c>
+      <c r="D212" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E212" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F212" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="0">
+        <v>355</v>
+      </c>
+      <c r="B213" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C213" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="D213" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E213" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F213" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="B214" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="C214" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="D214" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E214" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F214" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="B215" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="C215" t="s" s="0">
+        <v>359</v>
+      </c>
+      <c r="D215" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E215" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F215" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="B216" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="C216" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="D216" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E216" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F216" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="0">
+        <v>360</v>
+      </c>
+      <c r="B217" t="s" s="0">
+        <v>361</v>
+      </c>
+      <c r="C217" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="D217" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E217" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F217" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="0">
+        <v>362</v>
+      </c>
+      <c r="B218" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="C218" t="s" s="0">
+        <v>363</v>
+      </c>
+      <c r="D218" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E218" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F218" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="0">
+        <v>364</v>
+      </c>
+      <c r="B219" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C219" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="D219" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E219" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F219" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="0">
+        <v>365</v>
+      </c>
+      <c r="B220" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="C220" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="D220" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="E220" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="F220" t="s" s="0">
+        <v>253</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
